--- a/results/reliability_eval/Llama-3-8B_P127_sample_15_tokens_0.1_temp_deductive_reasoning_scores_08-24-4.xlsx
+++ b/results/reliability_eval/Llama-3-8B_P127_sample_15_tokens_0.1_temp_deductive_reasoning_scores_08-24-4.xlsx
@@ -477,31 +477,31 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.5096624310101399</v>
+        <v>0.5118500106071704</v>
       </c>
       <c r="B2" t="n">
-        <v>0.7367868705910703</v>
+        <v>0.5298218018217919</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5096624310101399</v>
+        <v>0.5118500106071704</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7367868705910703</v>
+        <v>0.5298218018217919</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4878192786548581</v>
+        <v>0.4885982924456933</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7258731023079906</v>
+        <v>0.5405595072009558</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9972660762418175</v>
+        <v>0.9999179445305025</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9985692266121912</v>
+        <v>0.9998606370123398</v>
       </c>
       <c r="I2" t="n">
-        <v>0.735</v>
+        <v>0.513</v>
       </c>
     </row>
   </sheetData>
